--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,42 +3763,42 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,42 +4194,42 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54542.0</t>
+          <t>51617.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>45.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-10.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.89</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>91.67999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>101.91</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>111.26</t>
+          <t>111.08</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>99.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-136.04</t>
+          <t>-137.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5233790.0</t>
+          <t>4984403.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2309731.0</t>
+          <t>2820754.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1844425.0</t>
+          <t>2261178.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3953879.86</t>
+          <t>3861738.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>465306</t>
+          <t>559575</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-198733.5113556983</t>
+          <t>-121473.3345341895</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>121248.97</v>
+        <v>303457.64</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22862.0</t>
+          <t>54542.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-12.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>12.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>102.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>111.41</t>
+          <t>111.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>98.04</t>
+          <t>98.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.21</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-133.50</t>
+          <t>-136.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2099714.0</t>
+          <t>5233790.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1773950.4</t>
+          <t>2309731.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1403575.1</t>
+          <t>1844425.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3935122.22</t>
+          <t>3953879.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>370375</t>
+          <t>465306</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-256912.1438544184</t>
+          <t>-198733.5113556983</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-170099.49</v>
+        <v>121248.97</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9275.0</t>
+          <t>22862.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>26.39</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.69</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-12.01</t>
+          <t>-13.32</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>104.68</t>
+          <t>103.6</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>111.71</t>
+          <t>111.41</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>97.57</t>
+          <t>98.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-62.93</t>
+          <t>-46.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.63</t>
+          <t>-133.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188217.571635311</t>
+          <t>1188212.132947977</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>812501.0</t>
+          <t>2099714.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1576176.0</t>
+          <t>1773950.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1341970.8</t>
+          <t>1403575.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4059655.58</t>
+          <t>3935122.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>234205</t>
+          <t>370375</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-272696.2628382232</t>
+          <t>-256912.1438544184</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-244442.73</v>
+        <v>-170099.49</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>6.225765044189555</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-7.878027667352193</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-5.799230904818664</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>98.49</t>
+          <t>93.98</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,37 +5619,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>11666.647</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2845.366</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -5870,11 +5870,11 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-5531156.81</v>
+        <v>22614004.75</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,22 +5923,22 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,42 +5948,42 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,27 +6003,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -6301,11 +6301,11 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-9100221.25</v>
+        <v>-5531156.81</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,22 +6354,22 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,42 +6379,42 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,27 +6434,27 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,37 +6702,37 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>82573246.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>110626528.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
+          <t>-6992563.928557849</t>
         </is>
       </c>
       <c r="BC15" t="n">
@@ -6785,22 +6785,22 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6815,37 +6815,37 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,27 +6865,27 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>45.85</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3090.038</t>
+          <t>1598.435</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-20.86</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>47.01000000000001</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>50.61</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-5544.97</t>
+          <t>-428.50</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-99.89</t>
+          <t>-101.57</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>143160471.0</t>
+          <t>73812718.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>85714374.6</t>
+          <t>82573246.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>91043176.7</t>
+          <t>86844569.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>111062396.92</t>
+          <t>110626528.9</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-5328802</t>
+          <t>-4271323</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6156468.461377018</t>
+          <t>-6609353.506099968</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-8229434.25</v>
+        <v>-9100221.25</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,17 +7216,17 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7246,37 +7246,37 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1323.95</t>
+          <t>3090.038</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-14.18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-20.86</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.01000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.61</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-296.49</t>
+          <t>-5544.97</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-98.34</t>
+          <t>-99.89</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>61756087.0</t>
+          <t>143160471.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>74243287.4</t>
+          <t>85714374.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>91368709.4</t>
+          <t>91043176.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>110369139.04</t>
+          <t>111062396.92</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-17125422</t>
+          <t>-5328802</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5779565.590711372</t>
+          <t>-6156468.461377018</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-14121660.85</v>
+        <v>-8229434.25</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,67 +7647,67 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,27 +7727,27 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1641.377</t>
+          <t>1323.95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-13.8</t>
+          <t>-17.04</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-24.18</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.97</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>47.82000000000001</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.91</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>50.82</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-151.77</t>
+          <t>-296.49</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-97.10</t>
+          <t>-98.34</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>77339411.0</t>
+          <t>61756087.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>76218975.6</t>
+          <t>74243287.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>100521086.4</t>
+          <t>91368709.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>110940841.56</t>
+          <t>110369139.04</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-24302110</t>
+          <t>-17125422</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4262820.998960823</t>
+          <t>-5779565.590711372</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-13312884.09</v>
+        <v>-14121660.85</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,22 +8078,22 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,37 +8108,37 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,27 +8158,27 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1190.696</t>
+          <t>1641.377</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-16.83</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-28.90</t>
+          <t>-24.18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-18.97</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.82000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.82</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>48.16</t>
+          <t>48.13</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.82</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-78.42</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-96.00</t>
+          <t>-97.10</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>56797544.0</t>
+          <t>77339411.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>77871465.6</t>
+          <t>76218975.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>109517420.0</t>
+          <t>100521086.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>112276509.48</t>
+          <t>110940841.56</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-31645954</t>
+          <t>-24302110</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-2617354.981653595</t>
+          <t>-4262820.998960823</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-13351670.45</v>
+        <v>-13312884.09</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,67 +8509,67 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,27 +8589,27 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>46.75</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>47.0</t>
         </is>
       </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1903.353</t>
+          <t>1190.696</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-13.44</t>
+          <t>-20.02</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-28.90</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-19.22</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,52 +8767,52 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -8822,22 +8822,22 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>50.97</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-62.02</t>
+          <t>-78.42</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-95.22</t>
+          <t>-96.00</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>89518360.0</t>
+          <t>56797544.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>91115892.8</t>
+          <t>77871465.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>122087741.2</t>
+          <t>109517420.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>112843950.2</t>
+          <t>112276509.48</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-30971848</t>
+          <t>-31645954</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-665661.2608210484</t>
+          <t>-2617354.981653595</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-10729319.83</v>
+        <v>-13351670.45</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,67 +8940,67 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,27 +9020,27 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1772.474</t>
+          <t>1903.353</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-15.86</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-17.50</t>
+          <t>-19.22</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.18</t>
+          <t>48.16</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>51.04</t>
+          <t>50.97</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-62.02</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.22</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>85805035.0</t>
+          <t>89518360.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>96371978.8</t>
+          <t>91115892.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>135847972.2</t>
+          <t>122087741.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>113475793.24</t>
+          <t>112843950.2</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-39475993</t>
+          <t>-30971848</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1164094.841961886</t>
+          <t>-665661.2608210484</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-10105716.38</v>
+        <v>-10729319.83</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,42 +9396,42 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,27 +9451,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1453.883</t>
+          <t>1772.474</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-19.01</t>
+          <t>-19.03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-15.26</t>
+          <t>-17.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,37 +9644,37 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.54</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -9684,22 +9684,22 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>51.04</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-94.42</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>71634528.0</t>
+          <t>85805035.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>108494131.4</t>
+          <t>96371978.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>142818685.5</t>
+          <t>135847972.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>116592030.84</t>
+          <t>113475793.24</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-34324554</t>
+          <t>-39475993</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>3213151.426871953</t>
+          <t>1164094.841961886</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-8456079.609999999</v>
+        <v>-10105716.38</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,42 +9827,42 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9887,22 +9887,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1720.148</t>
+          <t>1453.883</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-19.61</t>
+          <t>-22.26</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-15.26</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,52 +10060,52 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>66.58</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.33</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>51.09</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>86.88</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.04</t>
+          <t>-94.42</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>561727297.7239131</t>
+          <t>561925318.8690304</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>85601861.0</t>
+          <t>71634528.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>124823197.2</t>
+          <t>108494131.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>149472684.1</t>
+          <t>142818685.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>122361615.98</t>
+          <t>116592030.84</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-24649486</t>
+          <t>-34324554</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>5334829.797230658</t>
+          <t>3213151.426871953</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-4279184.21</v>
+        <v>-8456079.609999999</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>2.320505199027632</t>
+          <t>-20.96440015894935</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-17.3179148409989</t>
+          <t>-15.62971093975026</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-2.182287644583323</t>
+          <t>2.302408958965422</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,42 +10258,42 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>100.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>-17.66%</t>
+          <t>-23.13%</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>-28.23%</t>
+          <t>-32.40%</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,27 +10313,27 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,162 +1024,162 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>1188956.751082251</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-233639.39</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1188212.132947977</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-251981.92</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,29 +3412,29 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
           <t>56.54</t>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54542.0</t>
+          <t>51617.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-14.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>45.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-10.04</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.89</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>91.67999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>101.91</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>111.26</t>
+          <t>111.08</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>99.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-136.04</t>
+          <t>-137.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5233790.0</t>
+          <t>4984403.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2309731.0</t>
+          <t>2820754.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1844425.0</t>
+          <t>2261178.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3953879.86</t>
+          <t>3861738.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>465306</t>
+          <t>559575</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-198733.5113556983</t>
+          <t>-121473.3345341895</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>121248.97</v>
+        <v>303457.64</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22862.0</t>
+          <t>54542.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>129</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-12.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>12.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>102.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>111.41</t>
+          <t>111.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>98.04</t>
+          <t>98.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.21</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-133.50</t>
+          <t>-136.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188212.132947977</t>
+          <t>1188956.751082251</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2099714.0</t>
+          <t>5233790.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1773950.4</t>
+          <t>2309731.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1403575.1</t>
+          <t>1844425.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3935122.22</t>
+          <t>3953879.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>370375</t>
+          <t>465306</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-256912.1438544184</t>
+          <t>-198733.5113556983</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-170099.49</v>
+        <v>121248.97</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -5870,11 +5870,11 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>22614004.75</v>
+        <v>25006978.53</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -6301,11 +6301,11 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-5531156.81</v>
+        <v>22614004.75</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -6732,11 +6732,11 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-9100221.25</v>
+        <v>-5531156.81</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,37 +7133,37 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>82573246.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>110626528.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
+          <t>-6992563.928557849</t>
         </is>
       </c>
       <c r="BC16" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,17 +7296,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3090.038</t>
+          <t>1598.435</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-14.18</t>
+          <t>-17.87</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-20.86</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>47.01000000000001</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>50.61</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-5544.97</t>
+          <t>-428.50</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-99.89</t>
+          <t>-101.57</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>143160471.0</t>
+          <t>73812718.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>85714374.6</t>
+          <t>82573246.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>91043176.7</t>
+          <t>86844569.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>111062396.92</t>
+          <t>110626528.9</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-5328802</t>
+          <t>-4271323</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6156468.461377018</t>
+          <t>-6609353.506099968</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-8229434.25</v>
+        <v>-9100221.25</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1323.95</t>
+          <t>3090.038</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-17.04</t>
+          <t>-17.99</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-20.86</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.01000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.61</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-296.49</t>
+          <t>-5544.97</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-98.34</t>
+          <t>-99.89</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>61756087.0</t>
+          <t>143160471.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>74243287.4</t>
+          <t>85714374.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>91368709.4</t>
+          <t>91043176.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>110369139.04</t>
+          <t>111062396.92</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-17125422</t>
+          <t>-5328802</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5779565.590711372</t>
+          <t>-6156468.461377018</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-14121660.85</v>
+        <v>-8229434.25</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1641.377</t>
+          <t>1323.95</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-24.18</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.97</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>47.82000000000001</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.91</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>50.82</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-151.77</t>
+          <t>-296.49</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-97.10</t>
+          <t>-98.34</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>77339411.0</t>
+          <t>61756087.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>76218975.6</t>
+          <t>74243287.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>100521086.4</t>
+          <t>91368709.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>110940841.56</t>
+          <t>110369139.04</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-24302110</t>
+          <t>-17125422</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4262820.998960823</t>
+          <t>-5779565.590711372</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-13312884.09</v>
+        <v>-14121660.85</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1190.696</t>
+          <t>1641.377</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-20.02</t>
+          <t>-20.82</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-28.90</t>
+          <t>-24.18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-18.97</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.82000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.82</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>48.16</t>
+          <t>48.13</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.82</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-78.42</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-96.00</t>
+          <t>-97.10</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>56797544.0</t>
+          <t>77339411.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>77871465.6</t>
+          <t>76218975.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>109517420.0</t>
+          <t>100521086.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>112276509.48</t>
+          <t>110940841.56</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-31645954</t>
+          <t>-24302110</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2617354.981653595</t>
+          <t>-4262820.998960823</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-13351670.45</v>
+        <v>-13312884.09</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>46.75</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>48.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1903.353</t>
+          <t>1190.696</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-24.04</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-28.90</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-19.22</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,52 +9198,52 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -9253,22 +9253,22 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>50.97</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-62.02</t>
+          <t>-78.42</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-95.22</t>
+          <t>-96.00</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>89518360.0</t>
+          <t>56797544.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>91115892.8</t>
+          <t>77871465.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>122087741.2</t>
+          <t>109517420.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>112843950.2</t>
+          <t>112276509.48</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-30971848</t>
+          <t>-31645954</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-665661.2608210484</t>
+          <t>-2617354.981653595</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-10729319.83</v>
+        <v>-13351670.45</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1772.474</t>
+          <t>1903.353</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-19.03</t>
+          <t>-20.44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-17.50</t>
+          <t>-19.22</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>48.18</t>
+          <t>48.16</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>51.04</t>
+          <t>50.97</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-62.02</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.22</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>85805035.0</t>
+          <t>89518360.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>96371978.8</t>
+          <t>91115892.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>135847972.2</t>
+          <t>122087741.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>113475793.24</t>
+          <t>112843950.2</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-39475993</t>
+          <t>-30971848</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1164094.841961886</t>
+          <t>-665661.2608210484</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-10105716.38</v>
+        <v>-10729319.83</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1453.883</t>
+          <t>1772.474</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-22.26</t>
+          <t>-23.01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-29.06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-15.26</t>
+          <t>-17.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,37 +10075,37 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.54</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>51.09</t>
+          <t>51.04</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-94.42</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>561925318.8690304</t>
+          <t>561638857.6062138</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>71634528.0</t>
+          <t>85805035.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>108494131.4</t>
+          <t>96371978.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>142818685.5</t>
+          <t>135847972.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>116592030.84</t>
+          <t>113475793.24</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-34324554</t>
+          <t>-39475993</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>3213151.426871953</t>
+          <t>1164094.841961886</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-8456079.609999999</v>
+        <v>-10105716.38</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10318,17 +10318,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-233639.39</v>
+        <v>-260559.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,162 +1455,162 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1188385.067723343</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-233639.39</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1188956.751082251</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-251981.92</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-9.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-9.32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-13.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54542.0</t>
+          <t>51617.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-15.29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>45.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-10.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.89</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>91.67999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>101.91</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>111.26</t>
+          <t>111.08</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>99.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-136.04</t>
+          <t>-137.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5233790.0</t>
+          <t>4984403.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2309731.0</t>
+          <t>2820754.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1844425.0</t>
+          <t>2261178.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3953879.86</t>
+          <t>3861738.8</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>465306</t>
+          <t>559575</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-198733.5113556983</t>
+          <t>-121473.3345341895</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>121248.97</v>
+        <v>303457.64</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -5870,11 +5870,11 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>25006978.53</v>
+        <v>22619267.16</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -6301,11 +6301,11 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>22614004.75</v>
+        <v>25006978.53</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -6732,11 +6732,11 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-5531156.81</v>
+        <v>22614004.75</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -7163,11 +7163,11 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-9100221.25</v>
+        <v>-5531156.81</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-17.87</t>
+          <t>-22.43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,37 +7564,37 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>82573246.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>110626528.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
+          <t>-6992563.928557849</t>
         </is>
       </c>
       <c r="BC17" t="n">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,17 +7727,17 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3090.038</t>
+          <t>1598.435</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-17.99</t>
+          <t>-22.43</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-20.86</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>47.01000000000001</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>50.61</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-5544.97</t>
+          <t>-428.50</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-99.89</t>
+          <t>-101.57</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>143160471.0</t>
+          <t>73812718.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>85714374.6</t>
+          <t>82573246.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>91043176.7</t>
+          <t>86844569.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>111062396.92</t>
+          <t>110626528.9</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-5328802</t>
+          <t>-4271323</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6156468.461377018</t>
+          <t>-6609353.506099968</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-8229434.25</v>
+        <v>-9100221.25</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1323.95</t>
+          <t>3090.038</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-22.56</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-20.86</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.01000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.61</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-296.49</t>
+          <t>-5544.97</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-98.34</t>
+          <t>-99.89</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>61756087.0</t>
+          <t>143160471.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>74243287.4</t>
+          <t>85714374.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>91368709.4</t>
+          <t>91043176.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>110369139.04</t>
+          <t>111062396.92</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-17125422</t>
+          <t>-5328802</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5779565.590711372</t>
+          <t>-6156468.461377018</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-14121660.85</v>
+        <v>-8229434.25</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1641.377</t>
+          <t>1323.95</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-20.82</t>
+          <t>-25.63</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-24.18</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.97</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>47.82000000000001</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.91</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>50.82</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-151.77</t>
+          <t>-296.49</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-97.10</t>
+          <t>-98.34</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>77339411.0</t>
+          <t>61756087.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>76218975.6</t>
+          <t>74243287.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>100521086.4</t>
+          <t>91368709.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>110940841.56</t>
+          <t>110369139.04</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-24302110</t>
+          <t>-17125422</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4262820.998960823</t>
+          <t>-5779565.590711372</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-13312884.09</v>
+        <v>-14121660.85</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1190.696</t>
+          <t>1641.377</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-24.04</t>
+          <t>-25.5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-28.90</t>
+          <t>-24.18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-18.97</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.82000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.82</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.16</t>
+          <t>48.13</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.82</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-78.42</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-96.00</t>
+          <t>-97.10</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>56797544.0</t>
+          <t>77339411.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>77871465.6</t>
+          <t>76218975.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>109517420.0</t>
+          <t>100521086.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>112276509.48</t>
+          <t>110940841.56</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-31645954</t>
+          <t>-24302110</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2617354.981653595</t>
+          <t>-4262820.998960823</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-13351670.45</v>
+        <v>-13312884.09</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>46.75</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>48.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1903.353</t>
+          <t>1190.696</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-20.44</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-28.90</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.22</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,52 +9629,52 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -9684,22 +9684,22 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>50.97</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-62.02</t>
+          <t>-78.42</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.22</t>
+          <t>-96.00</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>89518360.0</t>
+          <t>56797544.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>91115892.8</t>
+          <t>77871465.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>122087741.2</t>
+          <t>109517420.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>112843950.2</t>
+          <t>112276509.48</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-30971848</t>
+          <t>-31645954</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-665661.2608210484</t>
+          <t>-2617354.981653595</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-10729319.83</v>
+        <v>-13351670.45</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1772.474</t>
+          <t>1903.353</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-23.01</t>
+          <t>-25.1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-29.06</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-17.50</t>
+          <t>-19.22</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.60</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>48.18</t>
+          <t>48.16</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>51.04</t>
+          <t>50.97</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-62.02</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.22</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>561638857.6062138</t>
+          <t>561254013.3008658</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>85805035.0</t>
+          <t>89518360.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>96371978.8</t>
+          <t>91115892.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>135847972.2</t>
+          <t>122087741.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>113475793.24</t>
+          <t>112843950.2</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-39475993</t>
+          <t>-30971848</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1164094.841961886</t>
+          <t>-665661.2608210484</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-10105716.38</v>
+        <v>-10729319.83</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>47.85</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-260559.83</v>
+        <v>-276461.79</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-233639.39</v>
+        <v>-260559.83</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,162 +1886,162 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1187712.248201439</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-233639.39</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1188385.067723343</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-251981.92</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,62 +2515,62 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
+          <t>92.04</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>15.18%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>-2.36%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>85.54</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>33468</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>中光電-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>84.12</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>32725</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>中光電-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.39</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-9.56</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-13.74</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-15.29</t>
+          <t>-11.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188385.067723343</t>
+          <t>1187712.248201439</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,119 +5750,119 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-15.01</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>-4.03</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>39.17</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>46.09</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>47.16</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-79.73</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-2.56</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-122.93</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>560656054.685879</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>97513823.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>223966399.4</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>-8.08</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-12.80</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-4.08</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>40.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>49.38</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-101.87</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-118.36</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>561254013.3008658</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>196627836.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5870,11 +5870,11 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
+          <t>6329599.558410167</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>22619267.16</v>
+        <v>12948836.54</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -6301,11 +6301,11 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>25006978.53</v>
+        <v>22619267.16</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -6732,11 +6732,11 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>22614004.75</v>
+        <v>25006978.53</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -7163,11 +7163,11 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-5531156.81</v>
+        <v>22614004.75</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -7594,11 +7594,11 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-9100221.25</v>
+        <v>-5531156.81</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-22.43</t>
+          <t>-20.66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,37 +7995,37 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>82573246.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>110626528.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
+          <t>-6992563.928557849</t>
         </is>
       </c>
       <c r="BC18" t="n">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3090.038</t>
+          <t>1598.435</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-22.56</t>
+          <t>-20.66</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-20.86</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>47.01000000000001</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>50.61</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-5544.97</t>
+          <t>-428.50</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-99.89</t>
+          <t>-101.57</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>143160471.0</t>
+          <t>73812718.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>85714374.6</t>
+          <t>82573246.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>91043176.7</t>
+          <t>86844569.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>111062396.92</t>
+          <t>110626528.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-5328802</t>
+          <t>-4271323</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6156468.461377018</t>
+          <t>-6609353.506099968</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-8229434.25</v>
+        <v>-9100221.25</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1323.95</t>
+          <t>3090.038</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-25.63</t>
+          <t>-20.79</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-20.86</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.01000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.61</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-296.49</t>
+          <t>-5544.97</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-98.34</t>
+          <t>-99.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>61756087.0</t>
+          <t>143160471.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>74243287.4</t>
+          <t>85714374.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>91368709.4</t>
+          <t>91043176.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>110369139.04</t>
+          <t>111062396.92</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-17125422</t>
+          <t>-5328802</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-5779565.590711372</t>
+          <t>-6156468.461377018</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-14121660.85</v>
+        <v>-8229434.25</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1641.377</t>
+          <t>1323.95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-25.5</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-24.18</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.97</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>47.82000000000001</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.91</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>50.82</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-151.77</t>
+          <t>-296.49</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-97.10</t>
+          <t>-98.34</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>77339411.0</t>
+          <t>61756087.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>76218975.6</t>
+          <t>74243287.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>100521086.4</t>
+          <t>91368709.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>110940841.56</t>
+          <t>110369139.04</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-24302110</t>
+          <t>-17125422</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4262820.998960823</t>
+          <t>-5779565.590711372</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-13312884.09</v>
+        <v>-14121660.85</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1190.696</t>
+          <t>1641.377</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-23.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-28.90</t>
+          <t>-24.18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-18.97</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.82000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.82</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>48.16</t>
+          <t>48.13</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.82</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-78.42</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-96.00</t>
+          <t>-97.10</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>56797544.0</t>
+          <t>77339411.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>77871465.6</t>
+          <t>76218975.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>109517420.0</t>
+          <t>100521086.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>112276509.48</t>
+          <t>110940841.56</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-31645954</t>
+          <t>-24302110</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2617354.981653595</t>
+          <t>-4262820.998960823</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-13351670.45</v>
+        <v>-13312884.09</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>46.75</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>47.0</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>48.25</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1903.353</t>
+          <t>1190.696</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-25.1</t>
+          <t>-26.97</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-28.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.22</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,52 +10060,52 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.97</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-62.02</t>
+          <t>-78.42</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.22</t>
+          <t>-96.00</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>561254013.3008658</t>
+          <t>560656054.685879</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>89518360.0</t>
+          <t>56797544.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>91115892.8</t>
+          <t>77871465.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>122087741.2</t>
+          <t>109517420.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>112843950.2</t>
+          <t>112276509.48</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-30971848</t>
+          <t>-31645954</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-665661.2608210484</t>
+          <t>-2617354.981653595</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-10729319.83</v>
+        <v>-13351670.45</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI23"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>104.22</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>810164.4</t>
+          <t>676255.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2333587.64</t>
+          <t>2237649.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-276461.79</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-203335.1473709531</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-283207.9937717296</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>446832</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>21.18</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>85.2</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-260559.83</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-188812.811661721</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-276461.7899467224</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>480517</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>23.09</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>25.88</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>85.6</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-233639.39</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-172876.6337917207</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-260559.8276986149</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>528139</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>23.09</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,273 +2337,278 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>1186968.765086207</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-233639.3877835108</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>1136155</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>1187712.248201439</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-251981.92</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-232059.16</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-142987.8434661122</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-251981.9240553796</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>789636</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>31.76</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>28.53</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-230317.98</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-123170.7379044272</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-232059.1571560712</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1116375</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>34.71</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>31.76</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-175290.35</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-103372.8434950374</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-230317.9845443424</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>702772</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>34.71</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-113090.38</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-80291.90875880011</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-175290.3456510033</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>914371</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>34.85</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>35.88</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>89.9</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>93.4</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>89.1</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-11.29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-49263.07</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-63019.46568749043</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-113090.384887269</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>1185679</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>31.18</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>34.85</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>90.6</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>89.9</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>56196.13</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-53915.6621966216</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-49263.07005024608</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>1068845</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>31.18</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.21</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1187712.248201439</t>
+          <t>1186968.765086207</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>181021.17</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-54761.58804141716</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>56196.13221872458</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>1291202</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>中光電</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>27.79118773626352</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-2.044940352257788</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>25.44</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>92.04</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>15.18%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-2.36%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>32217</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>中光電-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>96.2</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>56.54</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5619,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2571.721</t>
+          <t>2470.734</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,7 +5709,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5719,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-35.52</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,17 +5810,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5770,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.89</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-63.99</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.93</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,17 +5900,17 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>223966399.4</t>
+          <t>218971148.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -5870,168 +5930,173 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>6329599.558410167</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>12948836.54</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>6199373.768452047</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>5483131.923682392</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>92544726</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>-24.45</t>
-        </is>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
+          <t>-25.65</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BK13" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BL13" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM13" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CB13" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CC13" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>38.05</t>
-        </is>
-      </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CJ13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6050,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,12 +6140,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6150,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,119 +6246,119 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-15.01</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>-4.03</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>39.17</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>46.09</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>47.16</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-79.73</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-2.56</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-122.93</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>560049092.1453238</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>97513823.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>223966399.4</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-8.08</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-12.80</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-4.08</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>40.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>49.38</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-101.87</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-118.36</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>560656054.685879</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>196627836.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA14" t="inlineStr">
         <is>
           <t>0</t>
@@ -6301,168 +6366,173 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>22619267.16</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>6329599.558410167</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>12948836.54170999</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>97513823</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>-25.55</t>
-        </is>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
+          <t>-24.45</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
+      <c r="BK14" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK14" t="inlineStr">
+      <c r="BL14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM14" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="BO14" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO14" t="inlineStr">
+      <c r="BP14" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA14" t="inlineStr">
+      <c r="CB14" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB14" t="inlineStr">
+      <c r="CC14" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>39.0</t>
-        </is>
-      </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI14" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6481,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,12 +6576,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6581,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,12 +6772,12 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -6732,168 +6802,173 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>25006978.53</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>5126101.925082927</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>22619267.15525979</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>196627836</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>-22.66</t>
-        </is>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
+          <t>-25.55</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="BK15" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK15" t="inlineStr">
+      <c r="BL15" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM15" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="BO15" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO15" t="inlineStr">
+      <c r="BP15" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW15" t="inlineStr">
+      <c r="BX15" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA15" t="inlineStr">
+      <c r="CB15" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB15" t="inlineStr">
+      <c r="CC15" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>40.35</t>
-        </is>
-      </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
+          <t>37.45</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH15" t="inlineStr">
+      <c r="CI15" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI15" t="inlineStr">
+      <c r="CJ15" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6912,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,12 +7012,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7012,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,12 +7208,12 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -7163,168 +7238,173 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>22614004.75</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1945526.428687133</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>25006978.52621445</t>
+        </is>
+      </c>
+      <c r="BD16" t="n">
+        <v>242462750</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>-20.08</t>
-        </is>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
+          <t>-22.66</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="BK16" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK16" t="inlineStr">
+      <c r="BL16" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM16" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="BO16" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW16" t="inlineStr">
+      <c r="BX16" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA16" t="inlineStr">
+      <c r="CB16" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB16" t="inlineStr">
+      <c r="CC16" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH16" t="inlineStr">
+      <c r="CI16" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI16" t="inlineStr">
+      <c r="CJ16" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7343,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,12 +7448,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7443,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,12 +7644,12 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -7594,168 +7674,173 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>-5531156.81</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2247464.861772379</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>22614004.75164205</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>465706606</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>-17.89</t>
-        </is>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
+          <t>-20.08</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
+      <c r="BK17" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK17" t="inlineStr">
+      <c r="BL17" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM17" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="BO17" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO17" t="inlineStr">
+      <c r="BP17" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ17" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW17" t="inlineStr">
+      <c r="BX17" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA17" t="inlineStr">
+      <c r="CB17" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB17" t="inlineStr">
+      <c r="CC17" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>41.3</t>
-        </is>
-      </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH17" t="inlineStr">
+      <c r="CI17" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI17" t="inlineStr">
+      <c r="CJ17" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7779,7 +7864,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,12 +7884,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-20.66</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7874,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,12 +8080,12 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -8025,168 +8110,173 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>-9100221.25</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6767732.064211367</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>-5531156.810305715</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
+        <v>117520982</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>-8.85</t>
-        </is>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
+          <t>-17.89</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="BK18" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK18" t="inlineStr">
+      <c r="BL18" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM18" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="BO18" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr">
+      <c r="BP18" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ18" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW18" t="inlineStr">
+      <c r="BX18" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA18" t="inlineStr">
+      <c r="CB18" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB18" t="inlineStr">
+      <c r="CC18" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
+          <t>41.3</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH18" t="inlineStr">
+      <c r="CI18" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI18" t="inlineStr">
+      <c r="CJ18" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8205,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8230,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-20.66</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8315,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,198 +8516,203 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>82573246.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>110626528.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>-9100221.25</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6992563.928557849</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-9100221.252076194</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
+      <c r="BH19" t="inlineStr">
         <is>
           <t>-8.85</t>
         </is>
       </c>
-      <c r="BH19" t="inlineStr">
+      <c r="BI19" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
+      <c r="BK19" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK19" t="inlineStr">
+      <c r="BL19" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM19" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN19" t="inlineStr">
+      <c r="BO19" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO19" t="inlineStr">
+      <c r="BP19" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ19" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR19" t="inlineStr">
+      <c r="BS19" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>6.58</t>
-        </is>
-      </c>
       <c r="BT19" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW19" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA19" t="inlineStr">
+      <c r="CB19" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB19" t="inlineStr">
+      <c r="CC19" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
-      </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>45.85</t>
         </is>
       </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
+      <c r="CH19" t="inlineStr">
         <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH19" t="inlineStr">
+      <c r="CI19" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI19" t="inlineStr">
+      <c r="CJ19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -8636,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3090.038</t>
+          <t>1598.435</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-20.79</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-20.86</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>47.01000000000001</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>50.61</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-5544.97</t>
+          <t>-428.50</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-99.89</t>
+          <t>-101.57</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,198 +8952,203 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>143160471.0</t>
+          <t>73812718.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>85714374.6</t>
+          <t>82573246.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>91043176.7</t>
+          <t>86844569.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>111062396.92</t>
+          <t>110626528.9</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-5328802</t>
+          <t>-4271323</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6156468.461377018</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>-8229434.25</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6609353.506099968</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-9100221.252076194</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>73812718</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>-8.75</t>
-        </is>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
+      <c r="BK20" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK20" t="inlineStr">
+      <c r="BL20" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM20" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN20" t="inlineStr">
+      <c r="BO20" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO20" t="inlineStr">
+      <c r="BP20" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP20" t="inlineStr">
+      <c r="BQ20" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
       <c r="BR20" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>6.58</t>
-        </is>
-      </c>
       <c r="BT20" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW20" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA20" t="inlineStr">
+      <c r="CB20" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB20" t="inlineStr">
+      <c r="CC20" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>47.05</t>
-        </is>
-      </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>46.65</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>45.85</t>
         </is>
       </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>45.9</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
+          <t>45.85</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH20" t="inlineStr">
+      <c r="CI20" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI20" t="inlineStr">
+      <c r="CJ20" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9067,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1323.95</t>
+          <t>3090.038</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.73</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-20.86</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.01000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.61</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-296.49</t>
+          <t>-5544.97</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-98.34</t>
+          <t>-99.89</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,198 +9388,203 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>61756087.0</t>
+          <t>143160471.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>74243287.4</t>
+          <t>85714374.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>91368709.4</t>
+          <t>91043176.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>110369139.04</t>
+          <t>111062396.92</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-17125422</t>
+          <t>-5328802</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-5779565.590711372</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-14121660.85</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6156468.461377018</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-8229434.250038072</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>143160471</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-6.46</t>
-        </is>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
+          <t>-8.75</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ21" t="inlineStr">
+      <c r="BK21" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK21" t="inlineStr">
+      <c r="BL21" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM21" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN21" t="inlineStr">
+      <c r="BO21" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO21" t="inlineStr">
+      <c r="BP21" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW21" t="inlineStr">
+      <c r="BX21" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA21" t="inlineStr">
+      <c r="CB21" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB21" t="inlineStr">
+      <c r="CC21" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
+          <t>45.9</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH21" t="inlineStr">
+      <c r="CI21" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI21" t="inlineStr">
+      <c r="CJ21" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9498,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1641.377</t>
+          <t>1323.95</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-23.68</t>
+          <t>-25.8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-24.18</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.97</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>47.82000000000001</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.91</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>50.82</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-151.77</t>
+          <t>-296.49</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-97.10</t>
+          <t>-98.34</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,198 +9824,203 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>77339411.0</t>
+          <t>61756087.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>76218975.6</t>
+          <t>74243287.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>100521086.4</t>
+          <t>91368709.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>110940841.56</t>
+          <t>110369139.04</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-24302110</t>
+          <t>-17125422</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4262820.998960823</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>-13312884.09</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-5779565.590711372</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-14121660.84533939</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>61756087</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-6.56</t>
-        </is>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
+          <t>-6.46</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ22" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK22" t="inlineStr">
+      <c r="BL22" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM22" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN22" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO22" t="inlineStr">
+      <c r="BP22" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ22" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW22" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA22" t="inlineStr">
+      <c r="CB22" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB22" t="inlineStr">
+      <c r="CC22" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
-      </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
+          <t>47.05</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH22" t="inlineStr">
+      <c r="CI22" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI22" t="inlineStr">
+      <c r="CJ22" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9929,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1190.696</t>
+          <t>1641.377</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-26.97</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-28.90</t>
+          <t>-24.18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-18.97</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.82000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.82</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>48.16</t>
+          <t>48.13</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.82</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-78.42</t>
+          <t>-151.77</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-96.00</t>
+          <t>-97.10</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,198 +10260,203 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>560656054.685879</t>
+          <t>560049092.1453238</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>56797544.0</t>
+          <t>77339411.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>77871465.6</t>
+          <t>76218975.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>109517420.0</t>
+          <t>100521086.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>112276509.48</t>
+          <t>110940841.56</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-31645954</t>
+          <t>-24302110</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-2617354.981653595</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
-        <v>-13351670.45</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4262820.998960823</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-13312884.09415057</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>77339411</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>2025/10/30</t>
         </is>
       </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>-4.08</t>
-        </is>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
+          <t>-6.56</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BJ23" t="inlineStr">
         <is>
           <t>正崴</t>
         </is>
       </c>
-      <c r="BJ23" t="inlineStr">
+      <c r="BK23" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK23" t="inlineStr">
+      <c r="BL23" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="BM23" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
           <t>-20.96440015894935</t>
         </is>
       </c>
-      <c r="BN23" t="inlineStr">
+      <c r="BO23" t="inlineStr">
         <is>
           <t>-15.62971093975026</t>
         </is>
       </c>
-      <c r="BO23" t="inlineStr">
+      <c r="BP23" t="inlineStr">
         <is>
           <t>2.302408958965422</t>
         </is>
       </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ23" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
           <t>57.18</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
           <t>-23.13%</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
+      <c r="BX23" t="inlineStr">
         <is>
           <t>-32.40%</t>
         </is>
       </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
+          <t>19161</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
           <t>系統及周邊產品40.32%、C產品零組件28.33%、能源服務管理19.60%、C產品零售11.74% (2024年)</t>
         </is>
       </c>
-      <c r="CA23" t="inlineStr">
+      <c r="CB23" t="inlineStr">
         <is>
           <t>正崴-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB23" t="inlineStr">
+      <c r="CC23" t="inlineStr">
         <is>
           <t>電子零組件業右下上市</t>
         </is>
       </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
+          <t>47.9</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>46.75</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>47.0</t>
         </is>
       </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
+      <c r="CH23" t="inlineStr">
         <is>
           <t>46.32</t>
         </is>
       </c>
-      <c r="CH23" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 連接線、其他電腦及週邊設備之零組件** 平面顯示器 - 其他零組件** 通信網路 - 線材** 連接器 - 連接器設計、組裝及製造** 運動科技 - 穿戴式裝置** 體驗科技 - ODM/OEM** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="CI23" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>676255.8</t>
+          <t>797567.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2237649.02</t>
+          <t>2222751.52</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>446832</v>
+        <v>1396196</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,24 +1272,24 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>85.1</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
           <t>56.54</t>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>104.22</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>810164.4</t>
+          <t>676255.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2333587.64</t>
+          <t>2237649.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>480517</v>
+        <v>446832</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>528139</v>
+        <v>480517</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1136155</v>
+        <v>528139</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,167 +2773,167 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1188270.522955524</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-233639.3877835108</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>1136155</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1186968.765086207</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-251981.9240553796</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>789636</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1116375</v>
+        <v>789636</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>702772</v>
+        <v>1116375</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-175290.3456510033</t>
+          <t>-230317.9845443424</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>914371</v>
+        <v>702772</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-113090.384887269</t>
+          <t>-175290.3456510033</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1185679</v>
+        <v>914371</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-49263.07005024608</t>
+          <t>-113090.384887269</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1068845</v>
+        <v>1185679</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,24 +5196,24 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
       <c r="CH11" t="inlineStr">
         <is>
           <t>56.54</t>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1186968.765086207</t>
+          <t>1188270.522955524</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>56196.13221872458</t>
+          <t>-49263.07005024608</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1291202</v>
+        <v>1068845</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2470.734</t>
+          <t>1355.348</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-35.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,119 +5810,119 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-15.41</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-4.17</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>37.89</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>44.79</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>46.74</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>48.66</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-49.67</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-2.90</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-131.17</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>559354372.5883621</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>51016187.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>136033064.4</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>-2.58</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-15.52</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-3.22</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-3.96</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>38.39</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>45.44</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>48.89</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-63.99</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-2.78</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-127.30</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>560049092.1453238</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>92544726.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>218971148.2</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5930,16 +5930,16 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>6199373.768452047</t>
+          <t>4784919.337608813</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5483131.923682392</t>
+          <t>-2994580.032028973</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>92544726</v>
+        <v>51016187</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-25.05</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>37.4</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2571.721</t>
+          <t>2470.734</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-35.52</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.89</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-63.99</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.93</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>223966399.4</t>
+          <t>218971148.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -6366,16 +6366,16 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>6329599.558410167</t>
+          <t>6199373.768452047</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>12948836.54170999</t>
+          <t>5483131.923682392</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>97513823</v>
+        <v>92544726</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,119 +6682,119 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-15.01</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>-4.03</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>39.17</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>46.09</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>47.16</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-79.73</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-2.56</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-122.93</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>559354372.5883621</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>97513823.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>223966399.4</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-8.08</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-12.80</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-4.08</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>40.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>49.38</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-101.87</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-118.36</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>560049092.1453238</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>196627836.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA15" t="inlineStr">
         <is>
           <t>0</t>
@@ -6802,16 +6802,16 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
+          <t>6329599.558410167</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>22619267.15525979</t>
+          <t>12948836.54170999</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>196627836</v>
+        <v>97513823</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -7238,16 +7238,16 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>25006978.52621445</t>
+          <t>22619267.15525979</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>242462750</v>
+        <v>196627836</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -7674,16 +7674,16 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>22614004.75164205</t>
+          <t>25006978.52621445</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>465706606</v>
+        <v>242462750</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -8110,16 +8110,16 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-5531156.810305715</t>
+          <t>22614004.75164205</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>117520982</v>
+        <v>465706606</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-9.55</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -8546,16 +8546,16 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-9100221.252076194</t>
+          <t>-5531156.810305715</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>117520982</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-21.62</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,37 +8952,37 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>82573246.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>110626528.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
+          <t>-6992563.928557849</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>73812718</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3090.038</t>
+          <t>1598.435</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-22.73</t>
+          <t>-21.62</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-20.86</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>47.01000000000001</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>50.61</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-5544.97</t>
+          <t>-428.50</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-99.89</t>
+          <t>-101.57</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>143160471.0</t>
+          <t>73812718.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>85714374.6</t>
+          <t>82573246.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>91043176.7</t>
+          <t>86844569.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>111062396.92</t>
+          <t>110626528.9</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-5328802</t>
+          <t>-4271323</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6156468.461377018</t>
+          <t>-6609353.506099968</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-8229434.250038072</t>
+          <t>-9100221.252076194</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>143160471</v>
+        <v>73812718</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1323.95</t>
+          <t>3090.038</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-25.8</t>
+          <t>-21.75</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-20.86</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.01000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.61</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-296.49</t>
+          <t>-5544.97</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-98.34</t>
+          <t>-99.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>61756087.0</t>
+          <t>143160471.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>74243287.4</t>
+          <t>85714374.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>91368709.4</t>
+          <t>91043176.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>110369139.04</t>
+          <t>111062396.92</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-17125422</t>
+          <t>-5328802</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-5779565.590711372</t>
+          <t>-6156468.461377018</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-14121660.84533939</t>
+          <t>-8229434.250038072</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>61756087</v>
+        <v>143160471</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1641.377</t>
+          <t>1323.95</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-24.8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-24.18</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-18.97</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>47.82000000000001</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.91</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.82</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-151.77</t>
+          <t>-296.49</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-97.10</t>
+          <t>-98.34</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>560049092.1453238</t>
+          <t>559354372.5883621</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>77339411.0</t>
+          <t>61756087.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>76218975.6</t>
+          <t>74243287.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>100521086.4</t>
+          <t>91368709.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>110940841.56</t>
+          <t>110369139.04</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-24302110</t>
+          <t>-17125422</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-4262820.998960823</t>
+          <t>-5779565.590711372</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-13312884.09415057</t>
+          <t>-14121660.84533939</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>77339411</v>
+        <v>61756087</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>101.99</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>797567.8</t>
+          <t>993448.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2222751.52</t>
+          <t>2145653.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1396196</v>
+        <v>2115557</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>676255.8</t>
+          <t>797567.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2237649.02</t>
+          <t>2222751.52</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>446832</v>
+        <v>1396196</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>104.22</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>810164.4</t>
+          <t>676255.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2333587.64</t>
+          <t>2237649.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>480517</v>
+        <v>446832</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,27 +2139,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>528139</v>
+        <v>480517</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1136155</v>
+        <v>528139</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>941766.6</t>
+          <t>931861.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2858383.84</t>
+          <t>2699451.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>789636</v>
+        <v>1136155</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3447,27 +3447,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1116375</v>
+        <v>789636</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>702772</v>
+        <v>1116375</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,27 +4319,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-175290.3456510033</t>
+          <t>-230317.9845443424</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>914371</v>
+        <v>702772</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,27 +4755,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-113090.384887269</t>
+          <t>-175290.3456510033</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1185679</v>
+        <v>914371</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1188270.522955524</t>
+          <t>1191114.455587393</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-49263.07005024608</t>
+          <t>-113090.384887269</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1068845</v>
+        <v>1185679</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1355.348</t>
+          <t>1331.985</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-35.00</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,67 +5810,67 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-15.41</t>
+          <t>-14.50</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.19</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>48.66</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-49.67</t>
+          <t>-36.38</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-131.17</t>
+          <t>-134.29</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>136033064.4</t>
+          <t>97760133.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -5930,16 +5930,16 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>4784919.337608813</t>
+          <t>2687551.635634194</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-2994580.032028973</t>
+          <t>-8847970.725226209</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>51016187</v>
+        <v>51098096</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-25.05</t>
+          <t>-23.76</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2470.734</t>
+          <t>1355.348</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-35.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,119 +6246,119 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-15.41</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-4.17</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>37.89</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>44.79</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>46.74</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>48.66</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-49.67</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-2.90</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-131.17</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>558661822.7625538</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>51016187.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>136033064.4</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-2.58</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-15.52</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-3.22</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-3.96</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>38.39</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>45.44</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>48.89</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-63.99</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-2.78</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-127.30</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>559354372.5883621</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>92544726.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>218971148.2</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA14" t="inlineStr">
         <is>
           <t>0</t>
@@ -6366,16 +6366,16 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>6199373.768452047</t>
+          <t>4784919.337608813</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>5483131.923682392</t>
+          <t>-2994580.032028973</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>92544726</v>
+        <v>51016187</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-25.05</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>37.4</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2571.721</t>
+          <t>2470.734</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-35.52</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.89</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-63.99</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.93</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,17 +6772,17 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>223966399.4</t>
+          <t>218971148.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -6802,16 +6802,16 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>6329599.558410167</t>
+          <t>6199373.768452047</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>12948836.54170999</t>
+          <t>5483131.923682392</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>97513823</v>
+        <v>92544726</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,119 +7118,119 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-15.01</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>-4.03</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>39.17</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>46.09</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>47.16</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-79.73</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-2.56</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-122.93</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>558661822.7625538</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>97513823.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>223966399.4</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-8.08</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-12.80</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>-4.08</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>40.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>49.38</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-101.87</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-118.36</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>559354372.5883621</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>196627836.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA16" t="inlineStr">
         <is>
           <t>0</t>
@@ -7238,16 +7238,16 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
+          <t>6329599.558410167</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>22619267.15525979</t>
+          <t>12948836.54170999</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>196627836</v>
+        <v>97513823</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -7674,16 +7674,16 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>25006978.52621445</t>
+          <t>22619267.15525979</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>242462750</v>
+        <v>196627836</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -8110,16 +8110,16 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>22614004.75164205</t>
+          <t>25006978.52621445</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>465706606</v>
+        <v>242462750</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -8546,16 +8546,16 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-5531156.810305715</t>
+          <t>22614004.75164205</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>117520982</v>
+        <v>465706606</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-21.62</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -8982,16 +8982,16 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-9100221.252076194</t>
+          <t>-5531156.810305715</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>117520982</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-21.62</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,37 +9388,37 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>82573246.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>110626528.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
+          <t>-6992563.928557849</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>73812718</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,17 +9556,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3090.038</t>
+          <t>1598.435</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-21.75</t>
+          <t>-19.56</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-20.86</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>47.01000000000001</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>50.61</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-5544.97</t>
+          <t>-428.50</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-99.89</t>
+          <t>-101.57</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>143160471.0</t>
+          <t>73812718.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>85714374.6</t>
+          <t>82573246.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>91043176.7</t>
+          <t>86844569.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>111062396.92</t>
+          <t>110626528.9</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-5328802</t>
+          <t>-4271323</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6156468.461377018</t>
+          <t>-6609353.506099968</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-8229434.250038072</t>
+          <t>-9100221.252076194</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>143160471</v>
+        <v>73812718</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1323.95</t>
+          <t>3090.038</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-24.8</t>
+          <t>-19.69</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-20.86</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.01000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.05</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.61</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-296.49</t>
+          <t>-5544.97</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-98.34</t>
+          <t>-99.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>559354372.5883621</t>
+          <t>558661822.7625538</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>61756087.0</t>
+          <t>143160471.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>74243287.4</t>
+          <t>85714374.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>91368709.4</t>
+          <t>91043176.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>110369139.04</t>
+          <t>111062396.92</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-17125422</t>
+          <t>-5328802</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-5779565.590711372</t>
+          <t>-6156468.461377018</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-14121660.84533939</t>
+          <t>-8229434.250038072</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>61756087</v>
+        <v>143160471</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>101.99</t>
+          <t>101.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>993448.2</t>
+          <t>1187172.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2145653.4</t>
+          <t>2058125.44</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2115557</v>
+        <v>1496761</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>101.99</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>797567.8</t>
+          <t>993448.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2222751.52</t>
+          <t>2145653.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1396196</v>
+        <v>2115557</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>102.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>676255.8</t>
+          <t>797567.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2237649.02</t>
+          <t>2222751.52</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>446832</v>
+        <v>1396196</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,24 +2144,24 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>85.1</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
       <c r="CH4" t="inlineStr">
         <is>
           <t>56.54</t>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>104.22</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>810164.4</t>
+          <t>676255.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2333587.64</t>
+          <t>2237649.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>480517</v>
+        <v>446832</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>91.96</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>105.02</t>
+          <t>104.22</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>854615.4</t>
+          <t>810164.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2414824.58</t>
+          <t>2333587.64</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>528139</v>
+        <v>480517</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1136155</v>
+        <v>528139</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>941766.6</t>
+          <t>931861.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2858383.84</t>
+          <t>2699451.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>789636</v>
+        <v>1136155</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1116375</v>
+        <v>789636</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>702772</v>
+        <v>1116375</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-175290.3456510033</t>
+          <t>-230317.9845443424</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>914371</v>
+        <v>702772</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1191114.455587393</t>
+          <t>1192622.362660944</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-113090.384887269</t>
+          <t>-175290.3456510033</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1185679</v>
+        <v>914371</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>107.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1331.985</t>
+          <t>1792.719</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-32.24</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-14.50</t>
+          <t>-12.51</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>44.19</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>46.38</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-36.38</t>
+          <t>-23.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-134.29</t>
+          <t>-136.45</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>97760133.6</t>
+          <t>72419946.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -5930,16 +5930,16 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>2687551.635634194</t>
+          <t>533776.835177609</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-8847970.725226209</t>
+          <t>-11311984.56733361</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>51098096</v>
+        <v>69926901</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-23.76</t>
+          <t>-21.87</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1355.348</t>
+          <t>1331.985</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-35.00</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,67 +6246,67 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-15.41</t>
+          <t>-14.50</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.19</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>48.66</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-49.67</t>
+          <t>-36.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-131.17</t>
+          <t>-134.29</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>136033064.4</t>
+          <t>97760133.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -6366,16 +6366,16 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4784919.337608813</t>
+          <t>2687551.635634194</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-2994580.032028973</t>
+          <t>-8847970.725226209</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>51016187</v>
+        <v>51098096</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-25.05</t>
+          <t>-23.76</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2470.734</t>
+          <t>1355.348</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-35.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,119 +6682,119 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-15.41</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-4.17</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>37.89</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>44.79</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>46.74</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>48.66</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-49.67</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-2.90</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-131.17</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>558011720.3681948</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>51016187.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>136033064.4</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-2.58</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-15.52</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-3.22</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-3.96</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>38.39</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>45.44</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>48.89</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-63.99</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-2.78</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-127.30</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>558661822.7625538</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>92544726.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>218971148.2</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA15" t="inlineStr">
         <is>
           <t>0</t>
@@ -6802,16 +6802,16 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>6199373.768452047</t>
+          <t>4784919.337608813</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>5483131.923682392</t>
+          <t>-2994580.032028973</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>92544726</v>
+        <v>51016187</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-25.05</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>37.4</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2571.721</t>
+          <t>2470.734</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-35.52</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,17 +7118,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.89</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-63.99</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-122.93</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>223966399.4</t>
+          <t>218971148.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -7238,16 +7238,16 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>6329599.558410167</t>
+          <t>6199373.768452047</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>12948836.54170999</t>
+          <t>5483131.923682392</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>97513823</v>
+        <v>92544726</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,119 +7554,119 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-15.01</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>-4.03</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>39.17</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>46.09</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>47.16</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-79.73</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-2.56</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-122.93</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>558011720.3681948</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>97513823.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>223966399.4</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-8.08</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-12.80</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>-4.08</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>40.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>49.38</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-101.87</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-118.36</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>558661822.7625538</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>196627836.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="BA17" t="inlineStr">
         <is>
           <t>0</t>
@@ -7674,16 +7674,16 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
+          <t>6329599.558410167</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>22619267.15525979</t>
+          <t>12948836.54170999</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>196627836</v>
+        <v>97513823</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -8110,16 +8110,16 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>25006978.52621445</t>
+          <t>22619267.15525979</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>242462750</v>
+        <v>196627836</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.57</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -8546,16 +8546,16 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>22614004.75164205</t>
+          <t>25006978.52621445</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>465706606</v>
+        <v>242462750</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -8982,16 +8982,16 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-5531156.810305715</t>
+          <t>22614004.75164205</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>117520982</v>
+        <v>465706606</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,12 +9192,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -9418,16 +9418,16 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-9100221.252076194</t>
+          <t>-5531156.810305715</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>117520982</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-19.56</t>
+          <t>-16.67</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.67</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,37 +9824,37 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>82573246.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>110626528.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
+          <t>-6992563.928557849</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -9863,7 +9863,7 @@
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>73812718</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,17 +9992,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3090.038</t>
+          <t>1598.435</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-19.69</t>
+          <t>-16.67</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-4.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-20.86</t>
+          <t>-20.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>47.01000000000001</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.67</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.61</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-5544.97</t>
+          <t>-428.50</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-99.89</t>
+          <t>-101.57</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>558661822.7625538</t>
+          <t>558011720.3681948</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>143160471.0</t>
+          <t>73812718.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>85714374.6</t>
+          <t>82573246.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>91043176.7</t>
+          <t>86844569.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>111062396.92</t>
+          <t>110626528.9</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-5328802</t>
+          <t>-4271323</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6156468.461377018</t>
+          <t>-6609353.506099968</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-8229434.250038072</t>
+          <t>-9100221.252076194</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>143160471</v>
+        <v>73812718</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>88.82</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>101.54</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>101.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1496761.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1187172.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1187172.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1020894.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2058125.44</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2058125.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-65418.32762892707</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1496761</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1496761.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>85.55999999999999</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>89.42</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>101.99</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>101.99</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2115557.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>993448.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>993448.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>962655.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2145653.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2145653.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-98962.45567306643</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2115557</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2115557.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>84.28</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>89.54</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>102.79</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>102.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1396196.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>797567.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>797567.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>869667.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>2222751.52</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>2222751.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-209647.8366049416</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1396196</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1396196.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>84.74</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>90.4</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>103.48</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>103.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>446832.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>676255.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>676255.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>836932.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2237649.02</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2237649.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-283207.9937717296</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>446832</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>446832.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>86.17999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>91.23</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>104.22</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>104.22</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>480517.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>810164.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>810164.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>921369.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2333587.64</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2333587.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-276461.7899467224</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>480517</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>480517.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>87.38000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>91.96</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>105.02</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>105.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>528139.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>854615.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>854615.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1048562.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2414824.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2414824.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-260559.8276986149</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>528139</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>528139.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>89.12</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>92.97</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>105.91</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>105.91</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1136155.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>931861.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>931861.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1494189.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2699451.5</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2699451.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-233639.3877835108</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1136155</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>90.53999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>93.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>106.84</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>106.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>789636.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>941766.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1903952.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2858383.84</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-251981.9240553796</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>789636</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>789636.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>107.48</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>107.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1116375.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>997608.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>997608.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2034960.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2909917.96</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2909917.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-232059.1571560712</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1116375</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1116375.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>91.28</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>95.66</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>108.04</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>108.04</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>702772.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1032573.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1032573.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2004573.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>3051992.38</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>3051992.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-230317.9845443424</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>702772</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>702772.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>92.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>96.23</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>108.66</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>96.23</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>108.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>914371.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1242510.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1242510.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2031632.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>3137803.82</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>3137803.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-175290.3456510033</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>914371</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>914371.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>38.15</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>46.38</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>46.38</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>69926901.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>72419946.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>72419946.59999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-11311984.56733361</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>69926901</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>69926901.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>37.78</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>44.19</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>46.53</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>46.53</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>51098096.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>97760133.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>97760133.59999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-8847970.725226209</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>51098096</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>51098096.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>37.89</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>44.79</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>46.74</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>46.74</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>51016187.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>136033064.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>136033064.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2994580.032028973</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>51016187</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>51016187.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>38.39</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>45.44</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>46.96</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>92544726.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>218971148.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>218971148.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>5483131.923682392</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>92544726</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>92544726.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>39.17</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>46.09</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>47.16</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>47.16</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>97513823.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>223966399.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>223966399.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>12948836.54170999</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>97513823</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>97513823.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>40.73999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>47.36</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>196627836.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>0</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>22619267.15525979</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>196627836</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>196627836.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>42.42</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>47.33</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>47.57</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>47.57</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>242462750.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>0</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>25006978.52621445</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>242462750</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>242462750.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>43.82</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>47.83</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>47.73</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>47.73</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>465706606.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>0</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>22614004.75164205</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>465706606</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>465706606.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>45.19</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>48.21</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>47.86</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>47.86</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>117520982.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>0</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-5531156.810305715</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>117520982</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>117520982.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>46.33</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>48.58</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>47.96</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>47.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>0</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-9100221.252076194</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>0</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>46.81</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>48.67</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>73812718.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>82573246.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>82573246.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>86844569.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>110626528.9</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>110626528.9</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-9100221.252076194</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>73812718</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>73812718.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>89.97</v>
+        <v>90.31</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.54</v>
+        <v>101.05</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.87</t>
+          <t>103.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.80</t>
+          <t>-133.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1187172.6</v>
+        <v>2303736</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1020894.0</t>
+          <t>1556950.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2058125.44</v>
+        <v>2122460.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>166278</t>
+          <t>746785</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-169225.5414975917</t>
+          <t>-96699.92046831697</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-65418.32762892707</t>
+          <t>302190.9951926938</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN4" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>854615.4</v>
+        <v>810164.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2414824.58</v>
+        <v>2333587.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>92.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.91</v>
+        <v>105.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>931861.8</v>
+        <v>854615.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2699451.5</v>
+        <v>2414824.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>93.86</v>
+        <v>92.97</v>
       </c>
       <c r="AN9" t="n">
-        <v>106.84</v>
+        <v>105.91</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>941766.6</v>
+        <v>931861.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2858383.84</v>
+        <v>2699451.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>94.7</v>
+        <v>93.86</v>
       </c>
       <c r="AN10" t="n">
-        <v>107.48</v>
+        <v>106.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>997608.4</v>
+        <v>941766.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2909917.96</v>
+        <v>2858383.84</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,24 +4641,24 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="BU10" t="inlineStr">
         <is>
           <t>25.44</t>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>95.66</v>
+        <v>94.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>108.04</v>
+        <v>107.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1032573.8</v>
+        <v>997608.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3051992.38</v>
+        <v>2909917.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>96.23</v>
+        <v>95.66</v>
       </c>
       <c r="AN12" t="n">
-        <v>108.66</v>
+        <v>108.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1192622.362660944</t>
+          <t>1203911.475</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1242510.4</v>
+        <v>1032573.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3137803.82</v>
+        <v>3051992.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-175290.3456510033</t>
+          <t>-230317.9845443424</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>107.53</t>
+          <t>102.04</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>39098</t>
+          <t>37104</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1792.719</t>
+          <t>1639.587</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-54.65</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-32.24</t>
+          <t>-32.41</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-12.51</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>43.6</v>
+        <v>43.05</v>
       </c>
       <c r="AN13" t="n">
-        <v>46.38</v>
+        <v>46.2</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-23.73</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-136.45</t>
+          <t>-137.84</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69926901.0</t>
+          <t>63837721.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>72419946.59999999</v>
+        <v>65684726.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144825562.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-79140836</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>533776.835177609</t>
+          <t>-1580755.469099785</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-11311984.56733361</t>
+          <t>-13210683.14262545</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>69926901.0</t>
+          <t>63837721.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-21.87</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1331.985</t>
+          <t>1792.719</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-32.24</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-14.50</t>
+          <t>-12.51</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>44.19</v>
+        <v>43.6</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.53</v>
+        <v>46.38</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-36.38</t>
+          <t>-23.73</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-134.29</t>
+          <t>-136.45</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,16 +6260,16 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>97760133.59999999</v>
+        <v>72419946.59999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
@@ -6286,17 +6286,17 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>2687551.635634194</t>
+          <t>533776.835177609</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-8847970.725226209</t>
+          <t>-11311984.56733361</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-23.76</t>
+          <t>-21.87</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1355.348</t>
+          <t>1331.985</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-35.00</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,63 +6604,63 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-15.41</t>
+          <t>-14.50</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>44.79</v>
+        <v>44.19</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.74</v>
+        <v>46.53</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>48.66</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-49.67</t>
+          <t>-36.38</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-131.17</t>
+          <t>-134.29</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,16 +6690,16 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>136033064.4</v>
+        <v>97760133.59999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
@@ -6716,17 +6716,17 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4784919.337608813</t>
+          <t>2687551.635634194</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-2994580.032028973</t>
+          <t>-8847970.725226209</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-25.05</t>
+          <t>-23.76</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2470.734</t>
+          <t>1355.348</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-35.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-15.52</t>
+          <t>-15.41</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>45.44</v>
+        <v>44.79</v>
       </c>
       <c r="AN16" t="n">
-        <v>46.96</v>
+        <v>46.74</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>48.89</t>
+          <t>48.66</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-63.99</t>
+          <t>-49.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-131.17</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,16 +7120,16 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>92544726.0</t>
+          <t>51016187.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>218971148.2</v>
+        <v>136033064.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
@@ -7146,17 +7146,17 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>6199373.768452047</t>
+          <t>4784919.337608813</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>5483131.923682392</t>
+          <t>-2994580.032028973</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>92544726.0</t>
+          <t>51016187.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-25.05</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>37.4</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2571.721</t>
+          <t>2470.734</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-35.52</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>46.09</v>
+        <v>45.44</v>
       </c>
       <c r="AN17" t="n">
-        <v>47.16</v>
+        <v>46.96</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.89</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-63.99</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-122.93</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,16 +7550,16 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>223966399.4</v>
+        <v>218971148.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>6329599.558410167</t>
+          <t>6199373.768452047</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>12948836.54170999</t>
+          <t>5483131.923682392</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.73999999999999</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>46.72</v>
+        <v>46.09</v>
       </c>
       <c r="AN18" t="n">
-        <v>47.36</v>
+        <v>47.16</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-101.87</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-118.36</t>
+          <t>-122.93</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,16 +7980,16 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>196627836.0</t>
+          <t>97513823.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>223966399.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
+          <t>6329599.558410167</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>22619267.15525979</t>
+          <t>12948836.54170999</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>196627836.0</t>
+          <t>97513823.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>47.33</v>
+        <v>46.72</v>
       </c>
       <c r="AN19" t="n">
-        <v>47.57</v>
+        <v>47.36</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>25006978.52621445</t>
+          <t>22619267.15525979</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>47.83</v>
+        <v>47.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>47.73</v>
+        <v>47.57</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>22614004.75164205</t>
+          <t>25006978.52621445</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>26.94</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>48.21</v>
+        <v>47.83</v>
       </c>
       <c r="AN21" t="n">
-        <v>47.86</v>
+        <v>47.73</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-5531156.810305715</t>
+          <t>22614004.75164205</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>48.58</v>
+        <v>48.21</v>
       </c>
       <c r="AN22" t="n">
-        <v>47.96</v>
+        <v>47.86</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-9100221.252076194</t>
+          <t>-5531156.810305715</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1598.435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>48.67</v>
+        <v>48.58</v>
       </c>
       <c r="AN23" t="n">
-        <v>48</v>
+        <v>47.96</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>50.27</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-428.50</t>
+          <t>-206.32</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-101.57</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,33 +10130,33 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>558011720.3681948</t>
+          <t>557350411.1566525</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>82573246.2</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>86844569.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>110626528.9</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-4271323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6609353.506099968</t>
+          <t>-6992563.928557849</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>73812718.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61921.0</t>
+          <t>16328.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>90.68</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>90.31</v>
+        <v>90.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.05</v>
+        <v>100.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>103.99</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-133.54</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2303736</v>
+        <v>2521164.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1556950.2</t>
+          <t>1598710.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2122460.26</v>
+        <v>2048434.82</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>746785</t>
+          <t>922454</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-96699.92046831697</t>
+          <t>-49167.48712118959</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>302190.9951926938</t>
+          <t>212260.896288011</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>89.97</v>
+        <v>90.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.54</v>
+        <v>101.05</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.87</t>
+          <t>103.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-136.80</t>
+          <t>-133.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1187172.6</v>
+        <v>2303736</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1020894.0</t>
+          <t>1556950.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2058125.44</v>
+        <v>2122460.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>166278</t>
+          <t>746785</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-169225.5414975917</t>
+          <t>-96699.92046831697</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-65418.32762892707</t>
+          <t>302190.9951926938</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
       <c r="BU4" t="inlineStr">
         <is>
           <t>25.44</t>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN5" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>854615.4</v>
+        <v>810164.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2414824.58</v>
+        <v>2333587.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>92.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.91</v>
+        <v>105.02</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>931861.8</v>
+        <v>854615.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2699451.5</v>
+        <v>2414824.58</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,161 +4469,161 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>93.86</v>
+        <v>92.97</v>
       </c>
       <c r="AN10" t="n">
-        <v>106.84</v>
+        <v>105.91</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>1205476.457203994</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>931861.8</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2699451.5</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-233639.3877835108</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>1203911.475</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>941766.6</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2858383.84</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-251981.9240553796</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>94.7</v>
+        <v>93.86</v>
       </c>
       <c r="AN11" t="n">
-        <v>107.48</v>
+        <v>106.84</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>997608.4</v>
+        <v>941766.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2909917.96</v>
+        <v>2858383.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>95.66</v>
+        <v>94.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>108.04</v>
+        <v>107.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1203911.475</t>
+          <t>1205476.457203994</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1032573.8</v>
+        <v>997608.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3051992.38</v>
+        <v>2909917.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-230317.9845443424</t>
+          <t>-232059.1571560712</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>102.04</t>
+          <t>100.11</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1639.587</t>
+          <t>1199.037</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-54.65</t>
+          <t>-58.96</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-32.41</t>
+          <t>-32.50</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>43.05</v>
+        <v>42.54</v>
       </c>
       <c r="AN13" t="n">
-        <v>46.2</v>
+        <v>46.03</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-137.84</t>
+          <t>-138.60</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>63837721.0</t>
+          <t>46809595.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>65684726.2</v>
+        <v>56537700</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>144825562.8</t>
+          <t>137754424.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-79140836</t>
+          <t>-81216724</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1580755.469099785</t>
+          <t>-3720118.39950968</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-13210683.14262545</t>
+          <t>-15486614.5167641</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>63837721.0</t>
+          <t>46809595.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1792.719</t>
+          <t>1639.587</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-54.65</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-32.24</t>
+          <t>-32.41</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-12.51</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>43.6</v>
+        <v>43.05</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.38</v>
+        <v>46.2</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-23.73</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-136.45</t>
+          <t>-137.84</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69926901.0</t>
+          <t>63837721.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>72419946.59999999</v>
+        <v>65684726.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144825562.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-79140836</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>533776.835177609</t>
+          <t>-1580755.469099785</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-11311984.56733361</t>
+          <t>-13210683.14262545</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>69926901.0</t>
+          <t>63837721.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-21.87</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1331.985</t>
+          <t>1792.719</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-32.24</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-14.50</t>
+          <t>-12.51</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>44.19</v>
+        <v>43.6</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.53</v>
+        <v>46.38</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-36.38</t>
+          <t>-23.73</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-134.29</t>
+          <t>-136.45</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,16 +6690,16 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>97760133.59999999</v>
+        <v>72419946.59999999</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
@@ -6716,17 +6716,17 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>2687551.635634194</t>
+          <t>533776.835177609</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-8847970.725226209</t>
+          <t>-11311984.56733361</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-23.76</t>
+          <t>-21.87</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1355.348</t>
+          <t>1331.985</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-35.00</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,63 +7034,63 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-15.41</t>
+          <t>-14.50</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>44.79</v>
+        <v>44.19</v>
       </c>
       <c r="AN16" t="n">
-        <v>46.74</v>
+        <v>46.53</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>48.66</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-49.67</t>
+          <t>-36.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-131.17</t>
+          <t>-134.29</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,16 +7120,16 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>136033064.4</v>
+        <v>97760133.59999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
@@ -7146,17 +7146,17 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>4784919.337608813</t>
+          <t>2687551.635634194</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-2994580.032028973</t>
+          <t>-8847970.725226209</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-25.05</t>
+          <t>-23.76</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2470.734</t>
+          <t>1355.348</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-35.00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-15.52</t>
+          <t>-15.41</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>45.44</v>
+        <v>44.79</v>
       </c>
       <c r="AN17" t="n">
-        <v>46.96</v>
+        <v>46.74</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>48.89</t>
+          <t>48.66</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-63.99</t>
+          <t>-49.67</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-131.17</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,16 +7550,16 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>92544726.0</t>
+          <t>51016187.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>218971148.2</v>
+        <v>136033064.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>6199373.768452047</t>
+          <t>4784919.337608813</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5483131.923682392</t>
+          <t>-2994580.032028973</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>92544726.0</t>
+          <t>51016187.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-25.05</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>37.4</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2571.721</t>
+          <t>2470.734</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-35.52</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>46.09</v>
+        <v>45.44</v>
       </c>
       <c r="AN18" t="n">
-        <v>47.16</v>
+        <v>46.96</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.89</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-63.99</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-122.93</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,16 +7980,16 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>223966399.4</v>
+        <v>218971148.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>6329599.558410167</t>
+          <t>6199373.768452047</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>12948836.54170999</t>
+          <t>5483131.923682392</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.73999999999999</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>46.72</v>
+        <v>46.09</v>
       </c>
       <c r="AN19" t="n">
-        <v>47.36</v>
+        <v>47.16</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-101.87</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-118.36</t>
+          <t>-122.93</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,16 +8410,16 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>196627836.0</t>
+          <t>97513823.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>223966399.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
+          <t>6329599.558410167</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>22619267.15525979</t>
+          <t>12948836.54170999</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>196627836.0</t>
+          <t>97513823.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>47.33</v>
+        <v>46.72</v>
       </c>
       <c r="AN20" t="n">
-        <v>47.57</v>
+        <v>47.36</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>25006978.52621445</t>
+          <t>22619267.15525979</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>26.94</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>47.83</v>
+        <v>47.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>47.73</v>
+        <v>47.57</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>22614004.75164205</t>
+          <t>25006978.52621445</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>48.21</v>
+        <v>47.83</v>
       </c>
       <c r="AN22" t="n">
-        <v>47.86</v>
+        <v>47.73</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-5531156.810305715</t>
+          <t>22614004.75164205</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2845.366</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>48.58</v>
+        <v>48.21</v>
       </c>
       <c r="AN23" t="n">
-        <v>47.96</v>
+        <v>47.86</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-206.32</t>
+          <t>-183.18</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-105.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>557350411.1566525</t>
+          <t>556654502.5585715</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6992563.928557849</t>
+          <t>-6767732.064211367</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-9100221.252076194</t>
+          <t>-5531156.810305715</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117520982.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16328.0</t>
+          <t>10325.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>57.70</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.82</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>62.88</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>94.28</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>90.58</v>
+        <v>90.66</v>
       </c>
       <c r="AN2" t="n">
-        <v>100.73</v>
+        <v>100.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.09</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-127.29</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2521164.8</v>
+        <v>2433421</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1598710.3</t>
+          <t>1615494.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2048434.82</v>
+        <v>2025475.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>922454</t>
+          <t>817926</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-49167.48712118959</t>
+          <t>-26100.81531061689</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>212260.896288011</t>
+          <t>100765.8796475329</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>61921.0</t>
+          <t>16328.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>90.68</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>90.31</v>
+        <v>90.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>101.05</v>
+        <v>100.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>103.99</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-133.54</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2303736</v>
+        <v>2521164.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1556950.2</t>
+          <t>1598710.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2122460.26</v>
+        <v>2048434.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>746785</t>
+          <t>922454</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-96699.92046831697</t>
+          <t>-49167.48712118959</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>302190.9951926938</t>
+          <t>212260.896288011</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>89.97</v>
+        <v>90.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.54</v>
+        <v>101.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.87</t>
+          <t>103.99</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-136.80</t>
+          <t>-133.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1187172.6</v>
+        <v>2303736</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1020894.0</t>
+          <t>1556950.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2058125.44</v>
+        <v>2122460.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>166278</t>
+          <t>746785</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-169225.5414975917</t>
+          <t>-96699.92046831697</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-65418.32762892707</t>
+          <t>302190.9951926938</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>854615.4</v>
+        <v>810164.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2414824.58</v>
+        <v>2333587.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>92.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.91</v>
+        <v>105.02</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>931861.8</v>
+        <v>854615.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2699451.5</v>
+        <v>2414824.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>93.86</v>
+        <v>92.97</v>
       </c>
       <c r="AN11" t="n">
-        <v>106.84</v>
+        <v>105.91</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>941766.6</v>
+        <v>931861.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2858383.84</v>
+        <v>2699451.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>94.7</v>
+        <v>93.86</v>
       </c>
       <c r="AN12" t="n">
-        <v>107.48</v>
+        <v>106.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1205476.457203994</t>
+          <t>1205805.145299145</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>997608.4</v>
+        <v>941766.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2909917.96</v>
+        <v>2858383.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-232059.1571560712</t>
+          <t>-251981.9240553796</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>100.11</t>
+          <t>99.35</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1199.037</t>
+          <t>799.356</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-58.96</t>
+          <t>-44.27</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-32.50</t>
+          <t>-33.28</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>42.54</v>
+        <v>42.01</v>
       </c>
       <c r="AN13" t="n">
-        <v>46.03</v>
+        <v>45.84</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-138.60</t>
+          <t>-138.96</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,20 +5830,20 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46809595.0</t>
+          <t>31066389.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>56537700</v>
+        <v>52547740.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>137754424.1</t>
+          <t>94290402.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-81216724</t>
+          <t>-41742662</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3720118.39950968</t>
+          <t>-5897537.348160816</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-15486614.5167641</t>
+          <t>-17873341.56574206</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>46809595.0</t>
+          <t>31066389.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1639.587</t>
+          <t>1199.037</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-54.65</t>
+          <t>-58.96</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-32.41</t>
+          <t>-32.50</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>43.05</v>
+        <v>42.54</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.2</v>
+        <v>46.03</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-137.84</t>
+          <t>-138.60</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,20 +6260,20 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>63837721.0</t>
+          <t>46809595.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>65684726.2</v>
+        <v>56537700</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>144825562.8</t>
+          <t>137754424.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-79140836</t>
+          <t>-81216724</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1580755.469099785</t>
+          <t>-3720118.39950968</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-13210683.14262545</t>
+          <t>-15486614.5167641</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>63837721.0</t>
+          <t>46809595.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1792.719</t>
+          <t>1639.587</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-54.65</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-32.24</t>
+          <t>-32.41</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-12.51</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>43.6</v>
+        <v>43.05</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.38</v>
+        <v>46.2</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-23.73</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-136.45</t>
+          <t>-137.84</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,20 +6690,20 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69926901.0</t>
+          <t>63837721.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>72419946.59999999</v>
+        <v>65684726.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144825562.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-79140836</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>533776.835177609</t>
+          <t>-1580755.469099785</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-11311984.56733361</t>
+          <t>-13210683.14262545</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>69926901.0</t>
+          <t>63837721.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-21.87</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1331.985</t>
+          <t>1792.719</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-32.24</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-14.50</t>
+          <t>-12.51</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>44.19</v>
+        <v>43.6</v>
       </c>
       <c r="AN16" t="n">
-        <v>46.53</v>
+        <v>46.38</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-36.38</t>
+          <t>-23.73</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.29</t>
+          <t>-136.45</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,16 +7120,16 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>97760133.59999999</v>
+        <v>72419946.59999999</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
@@ -7146,17 +7146,17 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>2687551.635634194</t>
+          <t>533776.835177609</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-8847970.725226209</t>
+          <t>-11311984.56733361</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-23.76</t>
+          <t>-21.87</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1355.348</t>
+          <t>1331.985</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-35.00</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,58 +7469,58 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-15.41</t>
+          <t>-14.50</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>44.79</v>
+        <v>44.19</v>
       </c>
       <c r="AN17" t="n">
-        <v>46.74</v>
+        <v>46.53</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>48.66</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-49.67</t>
+          <t>-36.38</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-131.17</t>
+          <t>-134.29</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,16 +7550,16 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>136033064.4</v>
+        <v>97760133.59999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>4784919.337608813</t>
+          <t>2687551.635634194</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-2994580.032028973</t>
+          <t>-8847970.725226209</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-25.05</t>
+          <t>-23.76</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2470.734</t>
+          <t>1355.348</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-35.00</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-15.52</t>
+          <t>-15.41</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>45.44</v>
+        <v>44.79</v>
       </c>
       <c r="AN18" t="n">
-        <v>46.96</v>
+        <v>46.74</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>48.89</t>
+          <t>48.66</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-63.99</t>
+          <t>-49.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-131.17</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,16 +7980,16 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>92544726.0</t>
+          <t>51016187.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>218971148.2</v>
+        <v>136033064.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>6199373.768452047</t>
+          <t>4784919.337608813</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>5483131.923682392</t>
+          <t>-2994580.032028973</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>92544726.0</t>
+          <t>51016187.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-25.05</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>37.4</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2571.721</t>
+          <t>2470.734</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-35.52</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>46.09</v>
+        <v>45.44</v>
       </c>
       <c r="AN19" t="n">
-        <v>47.16</v>
+        <v>46.96</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.89</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-63.99</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-122.93</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,16 +8410,16 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>223966399.4</v>
+        <v>218971148.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>6329599.558410167</t>
+          <t>6199373.768452047</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>12948836.54170999</t>
+          <t>5483131.923682392</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.73999999999999</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>46.72</v>
+        <v>46.09</v>
       </c>
       <c r="AN20" t="n">
-        <v>47.36</v>
+        <v>47.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-101.87</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-118.36</t>
+          <t>-122.93</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,16 +8840,16 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>196627836.0</t>
+          <t>97513823.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>223966399.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
+          <t>6329599.558410167</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>22619267.15525979</t>
+          <t>12948836.54170999</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>196627836.0</t>
+          <t>97513823.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>47.33</v>
+        <v>46.72</v>
       </c>
       <c r="AN21" t="n">
-        <v>47.57</v>
+        <v>47.36</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>25006978.52621445</t>
+          <t>22619267.15525979</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>47.83</v>
+        <v>47.33</v>
       </c>
       <c r="AN22" t="n">
-        <v>47.73</v>
+        <v>47.57</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>22614004.75164205</t>
+          <t>25006978.52621445</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2845.366</t>
+          <t>11666.647</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-30.69</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>799</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>48.21</v>
+        <v>47.83</v>
       </c>
       <c r="AN23" t="n">
-        <v>47.86</v>
+        <v>47.73</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-183.18</t>
+          <t>-148.53</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-105.99</t>
+          <t>-109.52</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>556654502.5585715</t>
+          <t>555926892.117689</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6767732.064211367</t>
+          <t>-2247464.861772379</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-5531156.810305715</t>
+          <t>22614004.75164205</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>117520982.0</t>
+          <t>465706606.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.08</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10325.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.63</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.82</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.88</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>94.28</t>
+          <t>94.38000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>90.66</v>
+        <v>90.47</v>
       </c>
       <c r="AN2" t="n">
-        <v>100.32</v>
+        <v>99.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.29</t>
+          <t>-124.63</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>957477.0</t>
+          <t>475957.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2433421</v>
+        <v>2105501</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1615494.4</t>
+          <t>1549474.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2025475.02</v>
+        <v>1998402.46</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>817926</t>
+          <t>556026</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-26100.81531061689</t>
+          <t>-24533.5789539051</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>100765.8796475329</t>
+          <t>-15913.77899199026</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>957477.0</t>
+          <t>475957.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16328.0</t>
+          <t>10325.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>57.70</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>62.88</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>94.28</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>90.58</v>
+        <v>90.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>100.73</v>
+        <v>100.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.09</t>
+          <t>104.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.18</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-127.29</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2521164.8</v>
+        <v>2433421</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1598710.3</t>
+          <t>1615494.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2048434.82</v>
+        <v>2025475.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>922454</t>
+          <t>817926</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-49167.48712118959</t>
+          <t>-26100.81531061689</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>212260.896288011</t>
+          <t>100765.8796475329</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1533976.0</t>
+          <t>957477.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>61921.0</t>
+          <t>16328.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-20.59</t>
+          <t>-22.09</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>90.68</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>90.31</v>
+        <v>90.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>101.05</v>
+        <v>100.73</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>103.99</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-133.54</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2303736</v>
+        <v>2521164.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1556950.2</t>
+          <t>1598710.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2122460.26</v>
+        <v>2048434.82</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>746785</t>
+          <t>922454</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-96699.92046831697</t>
+          <t>-49167.48712118959</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>302190.9951926938</t>
+          <t>212260.896288011</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>6063334.0</t>
+          <t>1533976.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15006.0</t>
+          <t>61921.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.32</t>
+          <t>-20.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-10.63</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>89.97</v>
+        <v>90.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>101.54</v>
+        <v>101.05</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>103.87</t>
+          <t>103.99</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.80</t>
+          <t>-133.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1187172.6</v>
+        <v>2303736</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1020894.0</t>
+          <t>1556950.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2058125.44</v>
+        <v>2122460.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>166278</t>
+          <t>746785</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-169225.5414975917</t>
+          <t>-96699.92046831697</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-65418.32762892707</t>
+          <t>302190.9951926938</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1496761.0</t>
+          <t>6063334.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23366.0</t>
+          <t>15006.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-16.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>85.55999999999999</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>89.42</v>
+        <v>89.97</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.99</v>
+        <v>101.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>103.87</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.59</t>
+          <t>-136.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>993448.2</v>
+        <v>1187172.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>962655.0</t>
+          <t>1020894.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>2145653.4</v>
+        <v>2058125.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-188099.5803828034</t>
+          <t>-169225.5414975917</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-98962.45567306643</t>
+          <t>-65418.32762892707</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2115557.0</t>
+          <t>1496761.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16338.0</t>
+          <t>23366.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.79</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.9</t>
+          <t>-12.33</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>85.55999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>89.54000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>102.79</v>
+        <v>101.99</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>103.49</t>
+          <t>103.64</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-140.43</t>
+          <t>-139.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>797567.8</v>
+        <v>993448.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>869667.2</t>
+          <t>962655.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>2222751.52</v>
+        <v>2145653.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-72099</t>
+          <t>30793</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-204306.3303300283</t>
+          <t>-188099.5803828034</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-209647.8366049416</t>
+          <t>-98962.45567306643</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1396196.0</t>
+          <t>2115557.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5371.0</t>
+          <t>16338.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.20</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-31.05</t>
+          <t>-28.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-12.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>84.74</t>
+          <t>84.28</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>90.40000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>103.48</v>
+        <v>102.79</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>103.32</t>
+          <t>103.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-140.16</t>
+          <t>-140.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>676255.8</v>
+        <v>797567.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>836932.1</t>
+          <t>869667.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>2237649.02</v>
+        <v>2222751.52</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-160676</t>
+          <t>-72099</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-203335.1473709531</t>
+          <t>-204306.3303300283</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-283207.9937717296</t>
+          <t>-209647.8366049416</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>446832.0</t>
+          <t>1396196.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>85.1</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>81.9</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>82.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5650.0</t>
+          <t>5371.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-19.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-31.05</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.46</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>86.17999999999999</t>
+          <t>84.74</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>91.23</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>104.22</v>
+        <v>103.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.52</t>
+          <t>-140.16</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>810164.4</v>
+        <v>676255.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>921369.1</t>
+          <t>836932.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2333587.64</v>
+        <v>2237649.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-111204</t>
+          <t>-160676</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-188812.811661721</t>
+          <t>-203335.1473709531</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-276461.7899467224</t>
+          <t>-283207.9937717296</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>480517.0</t>
+          <t>446832.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6296.0</t>
+          <t>5650.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.44</t>
+          <t>-12.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>87.38000000000001</t>
+          <t>86.17999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>91.95999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.08</t>
+          <t>-139.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>854615.4</v>
+        <v>810164.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1048562.9</t>
+          <t>921369.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2414824.58</v>
+        <v>2333587.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-193947</t>
+          <t>-111204</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-172876.6337917207</t>
+          <t>-188812.811661721</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-260559.8276986149</t>
+          <t>-276461.7899467224</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>528139.0</t>
+          <t>480517.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>92.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>105.91</v>
+        <v>105.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>931861.8</v>
+        <v>854615.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2699451.5</v>
+        <v>2414824.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-233639.3877835108</t>
+          <t>-260559.8276986149</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>93.86</v>
+        <v>92.97</v>
       </c>
       <c r="AN12" t="n">
-        <v>106.84</v>
+        <v>105.91</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.11</t>
+          <t>-138.45</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1205805.145299145</t>
+          <t>1205105.472972973</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>941766.6</v>
+        <v>931861.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1903952.8</t>
+          <t>1494189.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2858383.84</v>
+        <v>2699451.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-962186</t>
+          <t>-562327</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-142987.8434661122</t>
+          <t>-156934.2348995581</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-251981.9240553796</t>
+          <t>-233639.3877835108</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>789636.0</t>
+          <t>1136155.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>99.35</t>
+          <t>98.39</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35775</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>799.356</t>
+          <t>883.335</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-44.27</t>
+          <t>-33.06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,53 +5759,53 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>76.32</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-8.34</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>39.01000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>42.01</v>
+        <v>41.56</v>
       </c>
       <c r="AN13" t="n">
-        <v>45.84</v>
+        <v>45.64</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>47.24</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,30 +5820,30 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-138.96</t>
+          <t>-138.95</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>31066389.0</t>
+          <t>34275028.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>52547740.4</v>
+        <v>49183126.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>94290402.4</t>
+          <t>73471630.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
@@ -5851,22 +5851,22 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-41742662</t>
+          <t>-24288503</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-5897537.348160816</t>
+          <t>-7891234.53088732</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-17873341.56574206</t>
+          <t>-18856569.03588308</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>31066389.0</t>
+          <t>34275028.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1199.037</t>
+          <t>799.356</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-58.96</t>
+          <t>-44.27</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-32.50</t>
+          <t>-33.28</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-8.34</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>42.54</v>
+        <v>42.01</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.03</v>
+        <v>45.84</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,30 +6250,30 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-138.60</t>
+          <t>-138.96</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46809595.0</t>
+          <t>31066389.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>56537700</v>
+        <v>52547740.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>137754424.1</t>
+          <t>94290402.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-81216724</t>
+          <t>-41742662</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3720118.39950968</t>
+          <t>-5897537.348160816</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-15486614.5167641</t>
+          <t>-17873341.56574206</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>46809595.0</t>
+          <t>31066389.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1639.587</t>
+          <t>1199.037</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-54.65</t>
+          <t>-58.96</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-32.41</t>
+          <t>-32.50</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>43.05</v>
+        <v>42.54</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.2</v>
+        <v>46.03</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-14.71</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,30 +6680,30 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-137.84</t>
+          <t>-138.60</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>63837721.0</t>
+          <t>46809595.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>65684726.2</v>
+        <v>56537700</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>144825562.8</t>
+          <t>137754424.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-79140836</t>
+          <t>-81216724</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1580755.469099785</t>
+          <t>-3720118.39950968</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-13210683.14262545</t>
+          <t>-15486614.5167641</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>63837721.0</t>
+          <t>46809595.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-22.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1792.719</t>
+          <t>1639.587</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-54.65</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-32.24</t>
+          <t>-32.41</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-12.51</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>43.6</v>
+        <v>43.05</v>
       </c>
       <c r="AN16" t="n">
-        <v>46.38</v>
+        <v>46.2</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-23.73</t>
+          <t>-14.71</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,30 +7110,30 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-136.45</t>
+          <t>-137.84</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69926901.0</t>
+          <t>63837721.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>72419946.59999999</v>
+        <v>65684726.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144825562.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
@@ -7141,22 +7141,22 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-79140836</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>533776.835177609</t>
+          <t>-1580755.469099785</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-11311984.56733361</t>
+          <t>-13210683.14262545</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>69926901.0</t>
+          <t>63837721.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-21.87</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1331.985</t>
+          <t>1792.719</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-32.24</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-14.50</t>
+          <t>-12.51</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>44.19</v>
+        <v>43.6</v>
       </c>
       <c r="AN17" t="n">
-        <v>46.53</v>
+        <v>46.38</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-36.38</t>
+          <t>-23.73</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,26 +7540,26 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-134.29</t>
+          <t>-136.45</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>97760133.59999999</v>
+        <v>72419946.59999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>2687551.635634194</t>
+          <t>533776.835177609</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-8847970.725226209</t>
+          <t>-11311984.56733361</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>51098096.0</t>
+          <t>69926901.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-23.76</t>
+          <t>-21.87</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1355.348</t>
+          <t>1331.985</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-35.00</t>
+          <t>-33.88</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,63 +7894,63 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-15.41</t>
+          <t>-14.50</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>44.79</v>
+        <v>44.19</v>
       </c>
       <c r="AN18" t="n">
-        <v>46.74</v>
+        <v>46.53</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>48.66</t>
+          <t>48.42</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-49.67</t>
+          <t>-36.38</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,26 +7970,26 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-131.17</t>
+          <t>-134.29</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>136033064.4</v>
+        <v>97760133.59999999</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
@@ -8006,17 +8006,17 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>4784919.337608813</t>
+          <t>2687551.635634194</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-2994580.032028973</t>
+          <t>-8847970.725226209</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>51016187.0</t>
+          <t>51098096.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-25.05</t>
+          <t>-23.76</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2470.734</t>
+          <t>1355.348</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-35.52</t>
+          <t>-35.00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-15.52</t>
+          <t>-15.41</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>45.44</v>
+        <v>44.79</v>
       </c>
       <c r="AN19" t="n">
-        <v>46.96</v>
+        <v>46.74</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>48.89</t>
+          <t>48.66</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-63.99</t>
+          <t>-49.67</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,26 +8400,26 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-131.17</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>92544726.0</t>
+          <t>51016187.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>218971148.2</v>
+        <v>136033064.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
@@ -8436,17 +8436,17 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>6199373.768452047</t>
+          <t>4784919.337608813</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>5483131.923682392</t>
+          <t>-2994580.032028973</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>92544726.0</t>
+          <t>51016187.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-25.65</t>
+          <t>-25.05</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>38.05</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>37.4</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2571.721</t>
+          <t>2470.734</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-35.52</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,17 +8754,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>-15.52</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>46.09</v>
+        <v>45.44</v>
       </c>
       <c r="AN20" t="n">
-        <v>47.16</v>
+        <v>46.96</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.89</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-63.99</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,26 +8830,26 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-122.93</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>223966399.4</v>
+        <v>218971148.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
@@ -8866,17 +8866,17 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>6329599.558410167</t>
+          <t>6199373.768452047</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>12948836.54170999</t>
+          <t>5483131.923682392</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>97513823.0</t>
+          <t>92544726.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-25.65</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.25</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5206.343</t>
+          <t>2571.721</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-35.43</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-15.01</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.73999999999999</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>46.72</v>
+        <v>46.09</v>
       </c>
       <c r="AN21" t="n">
-        <v>47.36</v>
+        <v>47.16</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-101.87</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,26 +9260,26 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-118.36</t>
+          <t>-122.93</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>196627836.0</t>
+          <t>97513823.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>223966399.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
@@ -9296,17 +9296,17 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>5126101.925082927</t>
+          <t>6329599.558410167</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>22619267.15525979</t>
+          <t>12948836.54170999</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>196627836.0</t>
+          <t>97513823.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6118.553</t>
+          <t>5206.343</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-32.93</t>
+          <t>-35.43</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-12.80</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>40.73999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>47.33</v>
+        <v>46.72</v>
       </c>
       <c r="AN22" t="n">
-        <v>47.57</v>
+        <v>47.36</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-121.63</t>
+          <t>-101.87</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,22 +9690,22 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-113.68</t>
+          <t>-118.36</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1945526.428687133</t>
+          <t>5126101.925082927</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>25006978.52621445</t>
+          <t>22619267.15525979</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>242462750.0</t>
+          <t>196627836.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11666.647</t>
+          <t>6118.553</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-30.69</t>
+          <t>-32.93</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>883</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>47.83</v>
+        <v>47.33</v>
       </c>
       <c r="AN23" t="n">
-        <v>47.73</v>
+        <v>47.57</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-148.53</t>
+          <t>-121.63</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-109.52</t>
+          <t>-113.68</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/10/13</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>555926892.117689</t>
+          <t>555208210.7072649</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-2247464.861772379</t>
+          <t>1945526.428687133</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>22614004.75164205</t>
+          <t>25006978.52621445</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>465706606.0</t>
+          <t>242462750.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-20.08</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/組裝廠.xlsx
+++ b/Result/checksun_type/組裝廠.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5182.0</t>
+          <t>9928.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-22.18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,54 +1014,54 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>60.23</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>56.44</t>
+          <t>56.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>94.38000000000001</t>
+          <t>92.98</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>90.47</v>
+        <v>90.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>99.95</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>46.42</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.63</t>
+          <t>-122.07</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>475957.0</t>
+          <t>914130.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2105501</v>
+        <v>1988974.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1549474.6</t>
+          <t>1588073.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1998402.46</v>
+        <v>1969999.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>556026</t>
+          <t>400901</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-24533.5789539051</t>
+          <t>-30655.90843251303</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-15913.77899199026</t>
+          <t>-64328.72056485666</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>475957.0</t>
+          <t>914130.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10325.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.63</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.82</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.88</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>94.28</t>
+          <t>94.38000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>90.66</v>
+        <v>90.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>100.32</v>
+        <v>99.95</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.13</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.29</t>
+          <t>-124.63</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1205105.472972973</t>
+          <t>1205341.395596591</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>957477.0</t>
+          <t>475957.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2433421</v>
+        <v>2105501</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1615494.4</t>
+          <t>1549474.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2025475.02</v>
+        <v>1998402.46</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>817926</t>
+          <t>556026</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-26100.81531061689</t>
+          <t>-24533.5789539051</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>100765.8796475329</t>
+          <t>-15913.77899199026</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>957477.0</t>
+          <t>475957.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16328.0</t>
+          <t>10325.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>57.70</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.09</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>56.82</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>62.88</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr